--- a/data/main/sheets/batch_04.xlsx
+++ b/data/main/sheets/batch_04.xlsx
@@ -467,19 +467,18 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_327</t>
+          <t xml:space="preserve">multiple_38</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Give me the schedule of Manchester United for the next 6 games in Premier League.</t>
+          <t xml:space="preserve">Find a book 'The Alchemist' in the library branches within New York city.</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_name = Manchester United
-num_of_games = 6
-league = Premier League</t>
+          <t xml:space="preserve">book_name = The Alchemist
+city = New York city</t>
         </is>
       </c>
       <c r="D3" s="6"/>
@@ -491,18 +490,19 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_71</t>
+          <t xml:space="preserve">multiple_140</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">How many veterans were there in the United States in the year 1954?</t>
+          <t xml:space="preserve">Find the lawsuits filed against the company Google in California in the year 2020.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">year = 1954
-category = veterans</t>
+          <t xml:space="preserve">company_name = Google
+location = California
+year = 2020</t>
         </is>
       </c>
       <c r="D4" s="6"/>
@@ -514,18 +514,18 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_144</t>
+          <t xml:space="preserve">simple_python_169</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the market performance of the S&amp;P 500 and the Dow Jones over the past 5 days.</t>
+          <t xml:space="preserve">Find the details of the court case identified by docket number 123456 in Texas. Don't return full text</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">indexes = S&amp;P 500, Dow Jones
-days = 5</t>
+          <t xml:space="preserve">docket_number = 123456
+location = Texas</t>
         </is>
       </c>
       <c r="D5" s="6"/>
@@ -537,18 +537,18 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_38</t>
+          <t xml:space="preserve">simple_python_189</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find a book 'The Alchemist' in the library branches within New York city.</t>
+          <t xml:space="preserve">Get weather information for New York, USA for the next 3 days with details.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">book_name = The Alchemist
-city = New York city</t>
+          <t xml:space="preserve">location = New York, USA
+days = 3</t>
         </is>
       </c>
       <c r="D6" s="6"/>
@@ -560,108 +560,15 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_398</t>
+          <t xml:space="preserve">multiple_191</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the opening hours of the Metropolitan Museum of Art on Saturday?</t>
+          <t xml:space="preserve">Book a luxury room in Hotel Paradise, Las Vegas, with a city view for 3 days starting from May 12, 2022.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">museum_name = Metropolitan Museum of Art
-day = Saturday</t>
-        </is>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">multiple_140</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Find the lawsuits filed against the company Google in California in the year 2020.</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">company_name = Google
-location = California
-year = 2020</t>
-        </is>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_169</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Find the details of the court case identified by docket number 123456 in Texas. Don't return full text</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">docket_number = 123456
-location = Texas</t>
-        </is>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simple_python_189</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Get weather information for New York, USA for the next 3 days with details.</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">location = New York, USA
-days = 3</t>
-        </is>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">multiple_191</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Book a luxury room in Hotel Paradise, Las Vegas, with a city view for 3 days starting from May 12, 2022.</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">hotel_name = Hotel Paradise
 location = Las Vegas
@@ -671,6 +578,98 @@
 view = city view</t>
         </is>
       </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simple_python_264</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find the size of the sculpture with title 'David' by Michelangelo.</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">artist = Michelangelo
+title = David
+detail = size</t>
+        </is>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">multiple_161</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find the top rated modern sculpture exhibition happening in New York in the upcoming month.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">location = New York
+art_form = modern sculpture</t>
+        </is>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simple_python_246</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who discovered Gravity and what was the method used?</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">discovery = Gravity</t>
+        </is>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">multiple_68</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Can I find a historical fiction book at the New York public library?</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">location = New York public library
+genre = historical fiction</t>
+        </is>
+      </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -680,19 +679,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_264</t>
+          <t xml:space="preserve">simple_python_372</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the size of the sculpture with title 'David' by Michelangelo.</t>
+          <t xml:space="preserve">Find the top five organic bananas brands on the basis of rating from Whole Foods store.</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">artist = Michelangelo
-title = David
-detail = size</t>
+          <t xml:space="preserve">product = bananas</t>
         </is>
       </c>
       <c r="D12" s="6"/>
@@ -704,18 +701,19 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_161</t>
+          <t xml:space="preserve">simple_python_37</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the top rated modern sculpture exhibition happening in New York in the upcoming month.</t>
+          <t xml:space="preserve">Find the estimated travel time by car from San Francisco to Los Angeles with stops at Santa Barbara and Monterey.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = New York
-art_form = modern sculpture</t>
+          <t xml:space="preserve">start_location = San Francisco
+end_location = Los Angeles
+stops = Santa Barbara, Monterey</t>
         </is>
       </c>
       <c r="D13" s="6"/>
@@ -727,17 +725,19 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_246</t>
+          <t xml:space="preserve">multiple_180</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who discovered Gravity and what was the method used?</t>
+          <t xml:space="preserve">Fetch player statistics of 'Zelda' on Switch for user 'Sam'.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">discovery = Gravity</t>
+          <t xml:space="preserve">game = Zelda
+username = Sam
+platform = Switch</t>
         </is>
       </c>
       <c r="D14" s="6"/>
@@ -749,18 +749,17 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_68</t>
+          <t xml:space="preserve">simple_python_14</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Can I find a historical fiction book at the New York public library?</t>
+          <t xml:space="preserve">Calculate the derivative of the function 3x^2 + 2x - 1.</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = New York public library
-genre = historical fiction</t>
+          <t xml:space="preserve">function = 3x^2 + 2x - 1</t>
         </is>
       </c>
       <c r="D15" s="6"/>
@@ -772,17 +771,18 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_372</t>
+          <t xml:space="preserve">simple_python_146</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the top five organic bananas brands on the basis of rating from Whole Foods store.</t>
+          <t xml:space="preserve">What's the price of Amazon stock for the last 3 days?</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">product = bananas</t>
+          <t xml:space="preserve">company = Amazon
+days = 3</t>
         </is>
       </c>
       <c r="D16" s="6"/>
@@ -794,19 +794,18 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_37</t>
+          <t xml:space="preserve">simple_python_232</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the estimated travel time by car from San Francisco to Los Angeles with stops at Santa Barbara and Monterey.</t>
+          <t xml:space="preserve">What was the full name king of England in 1800?</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_location = San Francisco
-end_location = Los Angeles
-stops = Santa Barbara, Monterey</t>
+          <t xml:space="preserve">location = England
+year = 1800</t>
         </is>
       </c>
       <c r="D17" s="6"/>
@@ -818,19 +817,19 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_180</t>
+          <t xml:space="preserve">simple_python_358</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fetch player statistics of 'Zelda' on Switch for user 'Sam'.</t>
+          <t xml:space="preserve">Find a gluten-free cookie recipe that takes less than 30 minutes to prepare.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game = Zelda
-username = Sam
-platform = Switch</t>
+          <t xml:space="preserve">diet = gluten-free
+time_limit = 30
+dish = cookie</t>
         </is>
       </c>
       <c r="D18" s="6"/>
@@ -842,17 +841,18 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_14</t>
+          <t xml:space="preserve">multiple_76</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calculate the derivative of the function 3x^2 + 2x - 1.</t>
+          <t xml:space="preserve">I want to order a custom bronze sculpture of a horse. What material options are available?</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">function = 3x^2 + 2x - 1</t>
+          <t xml:space="preserve">item = horse
+material = bronze</t>
         </is>
       </c>
       <c r="D19" s="6"/>
@@ -864,18 +864,18 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_118</t>
+          <t xml:space="preserve">simple_python_178</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find all movies starring Leonardo DiCaprio in the year 2010 from IMDB database.</t>
+          <t xml:space="preserve">Find details about lawsuit case numbered 'LAX2019080202' in the Los Angeles court.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_name = Leonardo DiCaprio
-year = 2010</t>
+          <t xml:space="preserve">case_number = LAX2019080202
+court_location = Los Angeles</t>
         </is>
       </c>
       <c r="D20" s="6"/>
@@ -887,18 +887,18 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_146</t>
+          <t xml:space="preserve">multiple_171</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's the price of Amazon stock for the last 3 days?</t>
+          <t xml:space="preserve">Who won the basketball game between Lakers and Clippers on Jan 28, 2021?</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">company = Amazon
-days = 3</t>
+          <t xml:space="preserve">teams = Lakers, Clippers
+date = Jan 28, 2021</t>
         </is>
       </c>
       <c r="D21" s="6"/>
@@ -910,18 +910,18 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_156</t>
+          <t xml:space="preserve">simple_python_265</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Look up details of a felony crime record for case number CA123456 in San Diego County</t>
+          <t xml:space="preserve">Find me sculptures near Chicago that were made in the 19th century.</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">case_number = CA123456
-county = San Diego County</t>
+          <t xml:space="preserve">location = Chicago
+time_frame = 19th century</t>
         </is>
       </c>
       <c r="D22" s="6"/>
@@ -933,18 +933,20 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_168</t>
+          <t xml:space="preserve">simple_python_317</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the lyrics to the song 'Bohemian Rhapsody' by Queen.</t>
+          <t xml:space="preserve">Find the ranking of LA Lakers in the NBA 2021 regular season.</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">song_title = Bohemian Rhapsody
-artist_name = Queen</t>
+          <t xml:space="preserve">team_name = LA Lakers
+league = NBA
+season = 2021
+type = regular</t>
         </is>
       </c>
       <c r="D23" s="6"/>
@@ -956,19 +958,19 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_358</t>
+          <t xml:space="preserve">multiple_16</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find a gluten-free cookie recipe that takes less than 30 minutes to prepare.</t>
+          <t xml:space="preserve">What's the required minimum population size (Ne) for maintaining the genetic diversity of a wild tiger population for the next 100 generations with a probability of 0.95?</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">diet = gluten-free
-time_limit = 30
-dish = cookie</t>
+          <t xml:space="preserve">species = wild tiger
+generations = 100
+probability = 0.95</t>
         </is>
       </c>
       <c r="D24" s="6"/>
@@ -980,18 +982,18 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_76</t>
+          <t xml:space="preserve">simple_python_349</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I want to order a custom bronze sculpture of a horse. What material options are available?</t>
+          <t xml:space="preserve">Find the highest score achieved by any player in the online game 'Overwatch' on PC globally.</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">item = horse
-material = bronze</t>
+          <t xml:space="preserve">game = Overwatch
+platform = PC</t>
         </is>
       </c>
       <c r="D25" s="6"/>
@@ -1003,18 +1005,18 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_178</t>
+          <t xml:space="preserve">multiple_59</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find details about lawsuit case numbered 'LAX2019080202' in the Los Angeles court.</t>
+          <t xml:space="preserve">Find lawyers specializing in criminal law near me in New York.</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">case_number = LAX2019080202
-court_location = Los Angeles</t>
+          <t xml:space="preserve">location = New York
+specialization = criminal law</t>
         </is>
       </c>
       <c r="D26" s="6"/>
@@ -1026,18 +1028,19 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_171</t>
+          <t xml:space="preserve">simple_python_225</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who won the basketball game between Lakers and Clippers on Jan 28, 2021?</t>
+          <t xml:space="preserve">What is the percentage of population preferring digital reading over physical books?</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">teams = Lakers, Clippers
-date = Jan 28, 2021</t>
+          <t xml:space="preserve">category = reading
+option_one = digital reading
+option_two = physical books</t>
         </is>
       </c>
       <c r="D27" s="6"/>
@@ -1049,18 +1052,19 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_265</t>
+          <t xml:space="preserve">simple_python_191</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me sculptures near Chicago that were made in the 19th century.</t>
+          <t xml:space="preserve">Find me the 5 tallest mountains within 50km of Denver, Colorado.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Chicago
-time_frame = 19th century</t>
+          <t xml:space="preserve">location = Denver, Colorado
+radius = 50
+amount = 5</t>
         </is>
       </c>
       <c r="D28" s="6"/>
@@ -1072,20 +1076,18 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_317</t>
+          <t xml:space="preserve">simple_python_159</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the ranking of LA Lakers in the NBA 2021 regular season.</t>
+          <t xml:space="preserve">Give me the details of Criminal Law Amendment Act of 2013.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_name = LA Lakers
-league = NBA
-season = 2021
-type = regular</t>
+          <t xml:space="preserve">act_name = Criminal Law Amendment Act
+amendment_year = 2013</t>
         </is>
       </c>
       <c r="D29" s="6"/>
@@ -1097,19 +1099,17 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_16</t>
+          <t xml:space="preserve">multiple_18</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's the required minimum population size (Ne) for maintaining the genetic diversity of a wild tiger population for the next 100 generations with a probability of 0.95?</t>
+          <t xml:space="preserve">Who were the main participants and what was the location of the Battle of Stalingrad?</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">species = wild tiger
-generations = 100
-probability = 0.95</t>
+          <t xml:space="preserve">battle = Battle of Stalingrad</t>
         </is>
       </c>
       <c r="D30" s="6"/>
@@ -1121,18 +1121,18 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_349</t>
+          <t xml:space="preserve">simple_python_221</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the highest score achieved by any player in the online game 'Overwatch' on PC globally.</t>
+          <t xml:space="preserve">What will be the population growth in London over the next five years?</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game = Overwatch
-platform = PC</t>
+          <t xml:space="preserve">location = London
+years = five</t>
         </is>
       </c>
       <c r="D31" s="6"/>
@@ -1144,18 +1144,18 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_59</t>
+          <t xml:space="preserve">multiple_114</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find lawyers specializing in criminal law near me in New York.</t>
+          <t xml:space="preserve">Get me the predictions of the evolutionary rate for Homo Sapiens for next 50 years using Darwin model</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = New York
-specialization = criminal law</t>
+          <t xml:space="preserve">species = Homo Sapiens
+years = 50</t>
         </is>
       </c>
       <c r="D32" s="6"/>
@@ -1167,19 +1167,19 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_225</t>
+          <t xml:space="preserve">simple_python_174</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the percentage of population preferring digital reading over physical books?</t>
+          <t xml:space="preserve">Get me the top 10 landmark cases in constitutional law in China.</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">category = reading
-option_one = digital reading
-option_two = physical books</t>
+          <t xml:space="preserve">field_of_law = constitutional law
+top_number = 10
+country = China</t>
         </is>
       </c>
       <c r="D33" s="6"/>
@@ -1191,18 +1191,18 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_193</t>
+          <t xml:space="preserve">multiple_23</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get me the travel distance and duration from the Eiffel Tower to the Louvre Museum</t>
+          <t xml:space="preserve">What are the current stats for basketball player LeBron James including points per game, assists, and minutes per game.</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_location = Eiffel Tower
-end_location = Louvre Museum</t>
+          <t xml:space="preserve">player_name = LeBron James
+stats_fields = points per game, assists, minutes per game</t>
         </is>
       </c>
       <c r="D34" s="6"/>
@@ -1214,19 +1214,18 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_204</t>
+          <t xml:space="preserve">simple_python_206</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find restaurants near me within 10 miles that offer Chinese cuisine in Seattle.</t>
+          <t xml:space="preserve">Find the nearest park with a tennis court in London.</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Seattle
-cuisine = Chinese
-max_distance = 10</t>
+          <t xml:space="preserve">location = London
+amenities = tennis court</t>
         </is>
       </c>
       <c r="D35" s="6"/>
@@ -1238,18 +1237,18 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_159</t>
+          <t xml:space="preserve">simple_python_141</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Give me the details of Criminal Law Amendment Act of 2013.</t>
+          <t xml:space="preserve">Get current Gold price per ounce.</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">act_name = Criminal Law Amendment Act
-amendment_year = 2013</t>
+          <t xml:space="preserve">metal = Gold
+measure = ounce</t>
         </is>
       </c>
       <c r="D36" s="6"/>
@@ -1261,17 +1260,18 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_18</t>
+          <t xml:space="preserve">multiple_70</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who were the main participants and what was the location of the Battle of Stalingrad?</t>
+          <t xml:space="preserve">Who were the kings of France during the 18th century?</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">battle = Battle of Stalingrad</t>
+          <t xml:space="preserve">country = France
+century = 18</t>
         </is>
       </c>
       <c r="D37" s="6"/>
@@ -1283,17 +1283,19 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_263</t>
+          <t xml:space="preserve">simple_python_202</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me the most recent art sculpture by James Plensa with detailed description.</t>
+          <t xml:space="preserve">How many greenhouse gas emissions would I save if I switched to renewable energy sources for 3 months in California?</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">artist_name = James Plensa</t>
+          <t xml:space="preserve">energy_type = renewable
+usage_duration = 3
+region = California</t>
         </is>
       </c>
       <c r="D38" s="6"/>
@@ -1305,18 +1307,19 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_114</t>
+          <t xml:space="preserve">multiple_137</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get me the predictions of the evolutionary rate for Homo Sapiens for next 50 years using Darwin model</t>
+          <t xml:space="preserve">Search for ongoing lawsuits related to the company 'Google' filed after January 1, 2021 in California.</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">species = Homo Sapiens
-years = 50</t>
+          <t xml:space="preserve">company = Google
+start_date = January 1, 2021
+location = California</t>
         </is>
       </c>
       <c r="D39" s="6"/>
@@ -1328,19 +1331,19 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_174</t>
+          <t xml:space="preserve">simple_python_362</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get me the top 10 landmark cases in constitutional law in China.</t>
+          <t xml:space="preserve">What are the top five sushi restaurants with high reviews i.e. above 4/5 in Tokyo?</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_of_law = constitutional law
-top_number = 10
-country = China</t>
+          <t xml:space="preserve">city = Tokyo
+top = 5
+review_rate = 4</t>
         </is>
       </c>
       <c r="D40" s="6"/>
@@ -1352,18 +1355,18 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_23</t>
+          <t xml:space="preserve">multiple_88</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the current stats for basketball player LeBron James including points per game, assists, and minutes per game.</t>
+          <t xml:space="preserve">Find me the number of active players in the game 'World of Warcraft' in 2020.</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">player_name = LeBron James
-stats_fields = points per game, assists, minutes per game</t>
+          <t xml:space="preserve">game_title = World of Warcraft
+year = 2020</t>
         </is>
       </c>
       <c r="D41" s="6"/>
@@ -1375,18 +1378,19 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_206</t>
+          <t xml:space="preserve">simple_python_268</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the nearest park with a tennis court in London.</t>
+          <t xml:space="preserve">Find me the sculptures of Michelangelo with material Marble in Rome, Italy.</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = London
-amenities = tennis court</t>
+          <t xml:space="preserve">artist = Michelangelo
+material = Marble
+location = Rome, Italy</t>
         </is>
       </c>
       <c r="D42" s="6"/>
